--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios184.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios184.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.71544892418053</v>
+        <v>24.28894936421344</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.53755838100135</v>
+        <v>27.33215798966395</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.38897947094891</v>
+        <v>31.48516825165636</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25.0686871814995</v>
+        <v>30.11308816562541</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27.93937684149025</v>
+        <v>29.55766263721313</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30.60862247711303</v>
+        <v>25.22509992323935</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>30.62485016008539</v>
+        <v>24.53336873209136</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>29.46987581047881</v>
+        <v>27.20293336489219</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25.77836773473798</v>
+        <v>31.2580643847412</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>24.88501232542105</v>
+        <v>30.24258472449463</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>28.59828815373391</v>
+        <v>29.43186407430457</v>
       </c>
     </row>
     <row r="13">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>30.18446668423915</v>
+        <v>25.51001669702502</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>30.91236932627262</v>
+        <v>24.41407287481404</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>29.43156602706526</v>
+        <v>27.46831218649313</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25.58005984573504</v>
+        <v>31.12054135913982</v>
       </c>
     </row>
     <row r="17">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25.00219695852805</v>
+        <v>30.11604075411575</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27.37453560532339</v>
+        <v>29.59217166275258</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>30.43166725599561</v>
+        <v>25.44455927718756</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>30.48748604861319</v>
+        <v>24.09982862144476</v>
       </c>
     </row>
     <row r="21">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>29.61336125400335</v>
+        <v>27.43730190074806</v>
       </c>
     </row>
     <row r="22">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25.63825655601422</v>
+        <v>31.19895641143234</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25.03789629901125</v>
+        <v>30.12672742577962</v>
       </c>
     </row>
     <row r="24">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>27.91651917294303</v>
+        <v>29.83564708856146</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30.55682105131695</v>
+        <v>25.58692349455116</v>
       </c>
     </row>
     <row r="26">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>27.62612017972637</v>
+        <v>25.42462019779553</v>
       </c>
     </row>
     <row r="27">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>28.40208159001697</v>
+        <v>27.2051570175227</v>
       </c>
     </row>
     <row r="28">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>21.56743235371911</v>
+        <v>26.86551536696615</v>
       </c>
     </row>
     <row r="29">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29.26324335824129</v>
+        <v>31.09296578891083</v>
       </c>
     </row>
     <row r="30">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>28.71145173452985</v>
+        <v>28.13863417924924</v>
       </c>
     </row>
     <row r="31">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30.20096854269094</v>
+        <v>25.41411119107351</v>
       </c>
     </row>
     <row r="32">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>27.37202424075402</v>
+        <v>25.69334256417962</v>
       </c>
     </row>
     <row r="33">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>28.27114356603083</v>
+        <v>27.58589429625777</v>
       </c>
     </row>
     <row r="34">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>21.76655711721586</v>
+        <v>27.01436773039142</v>
       </c>
     </row>
     <row r="35">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28.49841952299944</v>
+        <v>30.8360514641507</v>
       </c>
     </row>
     <row r="36">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>28.14371363491028</v>
+        <v>28.00798282490434</v>
       </c>
     </row>
     <row r="37">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>29.90146151238527</v>
+        <v>25.41215796429569</v>
       </c>
     </row>
     <row r="38">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>27.73876455874663</v>
+        <v>25.23386198799729</v>
       </c>
     </row>
     <row r="39">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>28.21606809705251</v>
+        <v>26.88380384229658</v>
       </c>
     </row>
     <row r="40">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>21.58281301651918</v>
+        <v>26.95230162068304</v>
       </c>
     </row>
     <row r="41">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>28.70664268178751</v>
+        <v>31.39000066788313</v>
       </c>
     </row>
     <row r="42">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>28.49659568393971</v>
+        <v>28.50726601362314</v>
       </c>
     </row>
     <row r="43">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>29.97573109505683</v>
+        <v>25.20480286392111</v>
       </c>
     </row>
     <row r="44">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>28.19214365076285</v>
+        <v>25.91994150474848</v>
       </c>
     </row>
     <row r="45">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>28.70109817525514</v>
+        <v>27.27025725687474</v>
       </c>
     </row>
     <row r="46">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>22.02841473124338</v>
+        <v>26.53671134862733</v>
       </c>
     </row>
     <row r="47">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>29.28064811074223</v>
+        <v>31.09180657723785</v>
       </c>
     </row>
     <row r="48">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>28.34101440091586</v>
+        <v>27.96531564403183</v>
       </c>
     </row>
     <row r="49">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>29.71446566507711</v>
+        <v>25.491584842882</v>
       </c>
     </row>
     <row r="50">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>30.89749435018505</v>
+        <v>26.24054184809708</v>
       </c>
     </row>
     <row r="51">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>26.96716243339586</v>
+        <v>28.26503234487279</v>
       </c>
     </row>
     <row r="52">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>25.36644349934741</v>
+        <v>28.62097162501428</v>
       </c>
     </row>
     <row r="53">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>26.12580479285424</v>
+        <v>29.75677016984944</v>
       </c>
     </row>
     <row r="54">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>25.63075465972433</v>
+        <v>25.84833674838088</v>
       </c>
     </row>
     <row r="55">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>22.60191611628591</v>
+        <v>26.43507566424254</v>
       </c>
     </row>
     <row r="56">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>31.3271785589043</v>
+        <v>26.30792008438094</v>
       </c>
     </row>
     <row r="57">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>26.6788064938182</v>
+        <v>28.32827705343842</v>
       </c>
     </row>
     <row r="58">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>25.29477447347506</v>
+        <v>29.34556011859102</v>
       </c>
     </row>
     <row r="59">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>26.63827777934602</v>
+        <v>30.11749388895881</v>
       </c>
     </row>
     <row r="60">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>25.57716112586458</v>
+        <v>26.22012039728236</v>
       </c>
     </row>
     <row r="61">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>22.62056859773373</v>
+        <v>26.49356793435362</v>
       </c>
     </row>
     <row r="62">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>31.4578883503109</v>
+        <v>26.50836081138378</v>
       </c>
     </row>
     <row r="63">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>26.44122168770994</v>
+        <v>28.63053614375105</v>
       </c>
     </row>
     <row r="64">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>25.36079146064021</v>
+        <v>28.65154984341622</v>
       </c>
     </row>
     <row r="65">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>26.61341140141514</v>
+        <v>29.72035776727477</v>
       </c>
     </row>
     <row r="66">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>25.520905305723</v>
+        <v>26.26350284795506</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>22.56879614192479</v>
+        <v>26.86724535644225</v>
       </c>
     </row>
     <row r="68">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>31.41694964032238</v>
+        <v>26.40632160470143</v>
       </c>
     </row>
     <row r="69">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>27.15865890972739</v>
+        <v>28.54107903251836</v>
       </c>
     </row>
     <row r="70">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>25.66042482864527</v>
+        <v>29.09804343441657</v>
       </c>
     </row>
     <row r="71">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>26.5819202369494</v>
+        <v>29.37367802378798</v>
       </c>
     </row>
     <row r="72">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>25.87833776380748</v>
+        <v>26.28976735529857</v>
       </c>
     </row>
     <row r="73">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>22.41283280967096</v>
+        <v>26.98551576878084</v>
       </c>
     </row>
     <row r="74">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>29.60901778962995</v>
+        <v>27.05026177912808</v>
       </c>
     </row>
     <row r="75">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>28.90212088698295</v>
+        <v>31.11769424065931</v>
       </c>
     </row>
     <row r="76">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>26.66481186217092</v>
+        <v>25.42974414431189</v>
       </c>
     </row>
     <row r="77">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>27.1867853823555</v>
+        <v>24.05744364283387</v>
       </c>
     </row>
     <row r="78">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>32.92373827306412</v>
+        <v>28.7541211203291</v>
       </c>
     </row>
     <row r="79">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>26.16606009958175</v>
+        <v>27.73574103665746</v>
       </c>
     </row>
     <row r="80">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>29.59216373821468</v>
+        <v>27.48047344023588</v>
       </c>
     </row>
     <row r="81">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>28.55575243525426</v>
+        <v>31.12573730246064</v>
       </c>
     </row>
     <row r="82">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>26.49430759106637</v>
+        <v>25.70713899156625</v>
       </c>
     </row>
     <row r="83">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>27.53283034969217</v>
+        <v>23.74375637562923</v>
       </c>
     </row>
     <row r="84">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>32.9037664015114</v>
+        <v>29.183001681852</v>
       </c>
     </row>
     <row r="85">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>26.24232211292819</v>
+        <v>27.50261411793268</v>
       </c>
     </row>
     <row r="86">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>30.13560549068074</v>
+        <v>26.7392304525257</v>
       </c>
     </row>
     <row r="87">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>28.51729931505649</v>
+        <v>31.07976440187982</v>
       </c>
     </row>
     <row r="88">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>26.28445089501654</v>
+        <v>25.50108654288849</v>
       </c>
     </row>
     <row r="89">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>27.6202367580223</v>
+        <v>23.72955454595091</v>
       </c>
     </row>
     <row r="90">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>32.81427463641549</v>
+        <v>29.48969802920528</v>
       </c>
     </row>
     <row r="91">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>26.18414068501485</v>
+        <v>27.82762757596359</v>
       </c>
     </row>
     <row r="92">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>29.220167606888</v>
+        <v>27.29593686046251</v>
       </c>
     </row>
     <row r="93">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>29.0401588385965</v>
+        <v>31.12466232603915</v>
       </c>
     </row>
     <row r="94">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>26.72405064660457</v>
+        <v>25.10045873813518</v>
       </c>
     </row>
     <row r="95">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>26.85793589141104</v>
+        <v>23.81034088503484</v>
       </c>
     </row>
     <row r="96">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>32.75319054756358</v>
+        <v>28.85093650092832</v>
       </c>
     </row>
     <row r="97">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>26.15974785817493</v>
+        <v>27.82500687980161</v>
       </c>
     </row>
     <row r="98">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>31.11888996427528</v>
+        <v>29.88714198756626</v>
       </c>
     </row>
     <row r="99">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>22.77562791290932</v>
+        <v>26.2179557222966</v>
       </c>
     </row>
     <row r="100">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.83663043544867</v>
+        <v>23.6186595060033</v>
       </c>
     </row>
     <row r="101">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>29.0583143318891</v>
+        <v>25.23739166511256</v>
       </c>
     </row>
     <row r="102">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>25.63227357308629</v>
+        <v>28.88315547917322</v>
       </c>
     </row>
     <row r="103">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>25.11696265682078</v>
+        <v>22.5997124855359</v>
       </c>
     </row>
     <row r="104">
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>30.99709143531456</v>
+        <v>29.35935870182558</v>
       </c>
     </row>
     <row r="105">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>22.85415847697323</v>
+        <v>26.55262308401528</v>
       </c>
     </row>
     <row r="106">
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.6551803687521</v>
+        <v>23.32556400563722</v>
       </c>
     </row>
     <row r="107">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>28.71678318914822</v>
+        <v>25.17628064709738</v>
       </c>
     </row>
     <row r="108">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>26.14062476629095</v>
+        <v>28.68856601687799</v>
       </c>
     </row>
     <row r="109">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>25.40971580339945</v>
+        <v>22.63242359964998</v>
       </c>
     </row>
     <row r="110">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>31.32954765213146</v>
+        <v>29.54145634898733</v>
       </c>
     </row>
     <row r="111">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>23.11863618558704</v>
+        <v>26.1664260282899</v>
       </c>
     </row>
     <row r="112">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.58305554226425</v>
+        <v>23.63054654503608</v>
       </c>
     </row>
     <row r="113">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>28.78265927766022</v>
+        <v>25.46988002891693</v>
       </c>
     </row>
     <row r="114">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>25.97536801798184</v>
+        <v>29.17925054498745</v>
       </c>
     </row>
     <row r="115">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>24.85471505383952</v>
+        <v>23.21567474866599</v>
       </c>
     </row>
     <row r="116">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>31.23701862737758</v>
+        <v>30.21016661728409</v>
       </c>
     </row>
     <row r="117">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>23.56840619130986</v>
+        <v>26.2489810079722</v>
       </c>
     </row>
     <row r="118">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.81628142134909</v>
+        <v>23.6205628618901</v>
       </c>
     </row>
     <row r="119">
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>29.20177060301521</v>
+        <v>25.22923773284905</v>
       </c>
     </row>
     <row r="120">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>25.78187221739299</v>
+        <v>28.79109643008636</v>
       </c>
     </row>
     <row r="121">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>25.41508075326358</v>
+        <v>22.67861026621567</v>
       </c>
     </row>
     <row r="122">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>27.92203012749242</v>
+        <v>32.57918242241904</v>
       </c>
     </row>
     <row r="123">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>32.70293748568328</v>
+        <v>25.20114303211475</v>
       </c>
     </row>
     <row r="124">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>27.74033583825441</v>
+        <v>26.28798841071341</v>
       </c>
     </row>
     <row r="125">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>28.54692676655198</v>
+        <v>28.61482164234168</v>
       </c>
     </row>
     <row r="126">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>32.93882028690867</v>
+        <v>32.63473253558949</v>
       </c>
     </row>
     <row r="127">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>27.28931343524161</v>
+        <v>30.36758871293025</v>
       </c>
     </row>
     <row r="128">
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>28.0713106773959</v>
+        <v>32.14240748901112</v>
       </c>
     </row>
     <row r="129">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>32.4756940803987</v>
+        <v>25.60075976190956</v>
       </c>
     </row>
     <row r="130">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>27.27622591126378</v>
+        <v>26.52768301615563</v>
       </c>
     </row>
     <row r="131">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>28.52900010321811</v>
+        <v>28.41628911122601</v>
       </c>
     </row>
     <row r="132">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>31.95213245348267</v>
+        <v>32.54374540082475</v>
       </c>
     </row>
     <row r="133">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>27.72439497618279</v>
+        <v>30.09839374539852</v>
       </c>
     </row>
     <row r="134">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>28.13703483602999</v>
+        <v>31.98365308159807</v>
       </c>
     </row>
     <row r="135">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>32.27571943380583</v>
+        <v>24.94958808801261</v>
       </c>
     </row>
     <row r="136">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>27.33003330110071</v>
+        <v>26.85197701874013</v>
       </c>
     </row>
     <row r="137">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>28.39763374935523</v>
+        <v>28.23746210529507</v>
       </c>
     </row>
     <row r="138">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>32.73473339583296</v>
+        <v>32.88725338390202</v>
       </c>
     </row>
     <row r="139">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>27.58742450232743</v>
+        <v>29.75533004682899</v>
       </c>
     </row>
     <row r="140">
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>27.92549366317779</v>
+        <v>31.40393719056339</v>
       </c>
     </row>
     <row r="141">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>32.17022646961986</v>
+        <v>25.37526888195785</v>
       </c>
     </row>
     <row r="142">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>27.74102775163145</v>
+        <v>26.69069187316985</v>
       </c>
     </row>
     <row r="143">
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>28.25879338229296</v>
+        <v>27.5674409319533</v>
       </c>
     </row>
     <row r="144">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>32.53045071465429</v>
+        <v>33.09587771176255</v>
       </c>
     </row>
     <row r="145">
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>27.47109532392664</v>
+        <v>30.13963212107637</v>
       </c>
     </row>
     <row r="146">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>27.75909285245015</v>
+        <v>30.94901064379287</v>
       </c>
     </row>
     <row r="147">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>31.26619757617619</v>
+        <v>29.06171138871566</v>
       </c>
     </row>
     <row r="148">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>21.39826549559779</v>
+        <v>21.96928819121501</v>
       </c>
     </row>
     <row r="149">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>28.3526697614701</v>
+        <v>24.82900557021475</v>
       </c>
     </row>
     <row r="150">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>25.21340136138838</v>
+        <v>27.6345461454959</v>
       </c>
     </row>
     <row r="151">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>27.27810744581255</v>
+        <v>28.26143221962824</v>
       </c>
     </row>
     <row r="152">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>28.2323276350775</v>
+        <v>30.87860049621005</v>
       </c>
     </row>
     <row r="153">
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>31.56779994496537</v>
+        <v>29.03274893710391</v>
       </c>
     </row>
     <row r="154">
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>21.6301516284225</v>
+        <v>21.83470066930731</v>
       </c>
     </row>
     <row r="155">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>28.38997011887107</v>
+        <v>24.55030530297532</v>
       </c>
     </row>
     <row r="156">
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>24.76315938330142</v>
+        <v>27.67110405047285</v>
       </c>
     </row>
     <row r="157">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>26.63084717916772</v>
+        <v>28.57130219594274</v>
       </c>
     </row>
     <row r="158">
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>27.6179243261499</v>
+        <v>30.99737112945293</v>
       </c>
     </row>
     <row r="159">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>31.40332820373069</v>
+        <v>29.03256133530195</v>
       </c>
     </row>
     <row r="160">
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>21.8600450791481</v>
+        <v>21.91462421514519</v>
       </c>
     </row>
     <row r="161">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>28.97082377267364</v>
+        <v>25.29950023086969</v>
       </c>
     </row>
     <row r="162">
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>25.13165009297809</v>
+        <v>27.44830008244776</v>
       </c>
     </row>
     <row r="163">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>26.5379365006848</v>
+        <v>29.05616539888272</v>
       </c>
     </row>
     <row r="164">
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>27.7430608061103</v>
+        <v>31.00097234762533</v>
       </c>
     </row>
     <row r="165">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>31.21621933247553</v>
+        <v>29.16588429288717</v>
       </c>
     </row>
     <row r="166">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>21.75690290846471</v>
+        <v>22.21559875202442</v>
       </c>
     </row>
     <row r="167">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>28.60604063174533</v>
+        <v>25.04155906485969</v>
       </c>
     </row>
     <row r="168">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>25.52228229917847</v>
+        <v>27.67764653788492</v>
       </c>
     </row>
     <row r="169">
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>26.90950551085671</v>
+        <v>29.3535548247309</v>
       </c>
     </row>
     <row r="170">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>29.24318450508686</v>
+        <v>29.60912636802953</v>
       </c>
     </row>
     <row r="171">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>32.43764741576997</v>
+        <v>30.31498807700212</v>
       </c>
     </row>
     <row r="172">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>20.03358911815186</v>
+        <v>30.22093722715295</v>
       </c>
     </row>
     <row r="173">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>26.25579934974277</v>
+        <v>26.0319339188768</v>
       </c>
     </row>
     <row r="174">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>32.98401237696219</v>
+        <v>30.43246701401886</v>
       </c>
     </row>
     <row r="175">
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>27.44458436619036</v>
+        <v>26.09688148731274</v>
       </c>
     </row>
     <row r="176">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>29.41582338798477</v>
+        <v>29.2931867608642</v>
       </c>
     </row>
     <row r="177">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>32.69073726682799</v>
+        <v>30.56430770027291</v>
       </c>
     </row>
     <row r="178">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>19.90921295682739</v>
+        <v>29.98727471190695</v>
       </c>
     </row>
     <row r="179">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>26.12582167105245</v>
+        <v>26.04376512606407</v>
       </c>
     </row>
     <row r="180">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>32.17174771206896</v>
+        <v>30.04842044126219</v>
       </c>
     </row>
     <row r="181">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>27.49927100959939</v>
+        <v>25.88400388675879</v>
       </c>
     </row>
     <row r="182">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>29.8095299580168</v>
+        <v>29.72772703268578</v>
       </c>
     </row>
     <row r="183">
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>32.89147465317112</v>
+        <v>30.57756271534462</v>
       </c>
     </row>
     <row r="184">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>20.19809862304406</v>
+        <v>29.73944982606726</v>
       </c>
     </row>
     <row r="185">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>26.1749346500388</v>
+        <v>25.89529676628444</v>
       </c>
     </row>
     <row r="186">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>33.01165030364098</v>
+        <v>30.41411688209458</v>
       </c>
     </row>
     <row r="187">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>27.06171612761496</v>
+        <v>25.75828917367987</v>
       </c>
     </row>
     <row r="188">
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>29.26032345086564</v>
+        <v>28.77971713167804</v>
       </c>
     </row>
     <row r="189">
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>32.11867163593841</v>
+        <v>30.00361764745363</v>
       </c>
     </row>
     <row r="190">
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>19.80790369707244</v>
+        <v>29.39377797087622</v>
       </c>
     </row>
     <row r="191">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>26.18494870148405</v>
+        <v>25.63006707805389</v>
       </c>
     </row>
     <row r="192">
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>32.6388088445372</v>
+        <v>29.74082693630269</v>
       </c>
     </row>
     <row r="193">
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>27.37433839758559</v>
+        <v>26.30878439798508</v>
       </c>
     </row>
   </sheetData>
